--- a/outputs/evaluation/architecture/validation/CF_M04/CF_M04_arch_eval_avg.xlsx
+++ b/outputs/evaluation/architecture/validation/CF_M04/CF_M04_arch_eval_avg.xlsx
@@ -447,10 +447,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8618</v>
+        <v>0.8529</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6757</v>
+        <v>0.6306</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -465,13 +465,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8515</v>
+        <v>0.8576</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7241</v>
+        <v>0.6897</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9624</v>
+        <v>0.9701</v>
       </c>
     </row>
     <row r="4">
@@ -481,13 +481,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9167</v>
+        <v>0.8333</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5</v>
+        <v>0.4167</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8665</v>
+        <v>0.885</v>
       </c>
     </row>
     <row r="7">
@@ -514,7 +514,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8393</v>
+        <v>0.8114</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -529,10 +529,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6987</v>
+        <v>0.7369</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8353</v>
+        <v>0.8372000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6425999999999999</v>
+        <v>0.7804</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2061</v>
+        <v>0.2092</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -638,16 +638,16 @@
         <v>21</v>
       </c>
       <c r="C2" t="n">
-        <v>18.6667</v>
+        <v>17.6667</v>
       </c>
       <c r="D2" t="n">
-        <v>16.6667</v>
+        <v>15.3333</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8944</v>
+        <v>0.8653999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7936</v>
+        <v>0.7301</v>
       </c>
     </row>
     <row r="3">
@@ -660,13 +660,13 @@
         <v>8</v>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>5.6667</v>
       </c>
       <c r="D3" t="n">
         <v>4.3333</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7222</v>
+        <v>0.7714</v>
       </c>
       <c r="F3" t="n">
         <v>0.5417</v>
@@ -682,16 +682,16 @@
         <v>8</v>
       </c>
       <c r="C4" t="n">
-        <v>4.3333</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>3.3333</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9167</v>
+        <v>0.8333</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5</v>
+        <v>0.4167</v>
       </c>
     </row>
   </sheetData>
@@ -737,7 +737,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>29</v>
+        <v>27.3333</v>
       </c>
     </row>
     <row r="4">
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25</v>
+        <v>23.3333</v>
       </c>
     </row>
     <row r="5">
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25</v>
+        <v>23.3333</v>
       </c>
     </row>
     <row r="6">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12</v>
+        <v>13.6667</v>
       </c>
     </row>
     <row r="8">
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8618</v>
+        <v>0.8529</v>
       </c>
     </row>
     <row r="9">
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6757</v>
+        <v>0.6306</v>
       </c>
     </row>
     <row r="10">

--- a/outputs/evaluation/architecture/validation/CF_M04/CF_M04_arch_eval_avg.xlsx
+++ b/outputs/evaluation/architecture/validation/CF_M04/CF_M04_arch_eval_avg.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,6 +436,11 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>f1</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>mean semantic meaning</t>
         </is>
       </c>
@@ -452,7 +457,10 @@
       <c r="C2" t="n">
         <v>0.6306</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" t="n">
+        <v>0.7241</v>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -471,6 +479,9 @@
         <v>0.6897</v>
       </c>
       <c r="D3" t="n">
+        <v>0.7631</v>
+      </c>
+      <c r="E3" t="n">
         <v>0.9701</v>
       </c>
     </row>
@@ -487,6 +498,9 @@
         <v>0.4167</v>
       </c>
       <c r="D4" t="n">
+        <v>0.5556</v>
+      </c>
+      <c r="E4" t="n">
         <v>0.885</v>
       </c>
     </row>
